--- a/docs/Silent-Auction-Import.xlsx
+++ b/docs/Silent-Auction-Import.xlsx
@@ -876,7 +876,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K29"/>
+  <dimension ref="A1:L29"/>
   <cols>
     <col min="1" max="1" width="30.83203125" customWidth="1"/>
     <col min="2" max="2" width="20.83203125" customWidth="1"/>
@@ -884,11 +884,12 @@
     <col min="4" max="4" width="11.83203125" customWidth="1"/>
     <col min="5" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.83203125" customWidth="1"/>
-    <col min="8" max="8" width="48.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="7.83203125" customWidth="1"/>
-    <col min="11" max="11" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="16.83203125" customWidth="1"/>
+    <col min="9" max="9" width="48.83203125" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" customWidth="1"/>
+    <col min="11" max="11" width="7.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -911,18 +912,21 @@
         <v>High Bidder</v>
       </c>
       <c r="G1" t="str">
+        <v>Cascade Start</v>
+      </c>
+      <c r="H1" t="str">
         <v>Last Bid Time</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Notes</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Winner Phone</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Paid?</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Picked Up?</v>
       </c>
     </row>
@@ -946,18 +950,21 @@
         <v>Matt Hershberger</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>7:00 PM</v>
       </c>
       <c r="H2" t="str">
+        <v/>
+      </c>
+      <c r="I2" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
       <c r="J2" t="str">
         <v/>
       </c>
       <c r="K2" t="str">
+        <v/>
+      </c>
+      <c r="L2" t="str">
         <v/>
       </c>
     </row>
@@ -984,15 +991,18 @@
         <v/>
       </c>
       <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
       <c r="J3" t="str">
         <v/>
       </c>
       <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
         <v/>
       </c>
     </row>
@@ -1019,15 +1029,18 @@
         <v/>
       </c>
       <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
       <c r="J4" t="str">
         <v/>
       </c>
       <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
         <v/>
       </c>
     </row>
@@ -1054,15 +1067,18 @@
         <v/>
       </c>
       <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
       <c r="J5" t="str">
         <v/>
       </c>
       <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
         <v/>
       </c>
     </row>
@@ -1089,15 +1105,18 @@
         <v/>
       </c>
       <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
       <c r="J6" t="str">
         <v/>
       </c>
       <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
         <v/>
       </c>
     </row>
@@ -1124,15 +1143,18 @@
         <v/>
       </c>
       <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
       <c r="J7" t="str">
         <v/>
       </c>
       <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
         <v/>
       </c>
     </row>
@@ -1159,15 +1181,18 @@
         <v/>
       </c>
       <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
       <c r="J8" t="str">
         <v/>
       </c>
       <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
         <v/>
       </c>
     </row>
@@ -1194,15 +1219,18 @@
         <v/>
       </c>
       <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
       <c r="J9" t="str">
         <v/>
       </c>
       <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
         <v/>
       </c>
     </row>
@@ -1229,15 +1257,18 @@
         <v/>
       </c>
       <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
       <c r="J10" t="str">
         <v/>
       </c>
       <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
         <v/>
       </c>
     </row>
@@ -1264,15 +1295,18 @@
         <v/>
       </c>
       <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
       <c r="J11" t="str">
         <v/>
       </c>
       <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
         <v/>
       </c>
     </row>
@@ -1299,15 +1333,18 @@
         <v/>
       </c>
       <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I12" t="str">
-        <v/>
-      </c>
       <c r="J12" t="str">
         <v/>
       </c>
       <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
         <v/>
       </c>
     </row>
@@ -1334,15 +1371,18 @@
         <v/>
       </c>
       <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
         <v>Lunch on Jul 23</v>
       </c>
-      <c r="I13" t="str">
-        <v/>
-      </c>
       <c r="J13" t="str">
         <v/>
       </c>
       <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
         <v/>
       </c>
     </row>
@@ -1366,18 +1406,21 @@
         <v>Matt Janzi</v>
       </c>
       <c r="G14" t="str">
-        <v/>
+        <v>7:20 PM</v>
       </c>
       <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
         <v>@ Peter's house 7/10 at 5:30. Campfire after, weather permitting</v>
       </c>
-      <c r="I14" t="str">
-        <v/>
-      </c>
       <c r="J14" t="str">
         <v/>
       </c>
       <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
         <v/>
       </c>
     </row>
@@ -1415,6 +1458,9 @@
       <c r="K15" t="str">
         <v/>
       </c>
+      <c r="L15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1450,6 +1496,9 @@
       <c r="K16" t="str">
         <v/>
       </c>
+      <c r="L16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1485,6 +1534,9 @@
       <c r="K17" t="str">
         <v/>
       </c>
+      <c r="L17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1506,18 +1558,21 @@
         <v>Aaron Troyer</v>
       </c>
       <c r="G18" t="str">
-        <v/>
+        <v>7:35 PM</v>
       </c>
       <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
         <v>Donated by Dennis · Sometime in July</v>
       </c>
-      <c r="I18" t="str">
-        <v/>
-      </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
         <v/>
       </c>
     </row>
@@ -1544,15 +1599,18 @@
         <v/>
       </c>
       <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
         <v>Donated by Dennis · Sometime in July</v>
       </c>
-      <c r="I19" t="str">
-        <v/>
-      </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
         <v/>
       </c>
     </row>
@@ -1579,15 +1637,18 @@
         <v/>
       </c>
       <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
         <v>Donated by Dennis · Sometime in July</v>
       </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
         <v/>
       </c>
     </row>
@@ -1611,18 +1672,21 @@
         <v>Dan D. I. Miller</v>
       </c>
       <c r="G21" t="str">
-        <v/>
+        <v>7:45 PM</v>
       </c>
       <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
         <v>Donated by Charles &amp; Gloria Kratzer</v>
       </c>
-      <c r="I21" t="str">
-        <v/>
-      </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
         <v/>
       </c>
     </row>
@@ -1649,15 +1713,18 @@
         <v/>
       </c>
       <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
         <v>Donated by Charles &amp; Gloria Kratzer</v>
       </c>
-      <c r="I22" t="str">
-        <v/>
-      </c>
       <c r="J22" t="str">
         <v/>
       </c>
       <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
         <v/>
       </c>
     </row>
@@ -1681,18 +1748,21 @@
         <v>Eric McGlumphy</v>
       </c>
       <c r="G23" t="str">
-        <v/>
+        <v>7:55 PM</v>
       </c>
       <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I23" t="str">
-        <v/>
-      </c>
       <c r="J23" t="str">
         <v/>
       </c>
       <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
         <v/>
       </c>
     </row>
@@ -1719,15 +1789,18 @@
         <v/>
       </c>
       <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I24" t="str">
-        <v/>
-      </c>
       <c r="J24" t="str">
         <v/>
       </c>
       <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
         <v/>
       </c>
     </row>
@@ -1754,15 +1827,18 @@
         <v/>
       </c>
       <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I25" t="str">
-        <v/>
-      </c>
       <c r="J25" t="str">
         <v/>
       </c>
       <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
         <v/>
       </c>
     </row>
@@ -1789,15 +1865,18 @@
         <v/>
       </c>
       <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I26" t="str">
-        <v/>
-      </c>
       <c r="J26" t="str">
         <v/>
       </c>
       <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
         <v/>
       </c>
     </row>
@@ -1824,15 +1903,18 @@
         <v/>
       </c>
       <c r="H27" t="str">
+        <v/>
+      </c>
+      <c r="I27" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I27" t="str">
-        <v/>
-      </c>
       <c r="J27" t="str">
         <v/>
       </c>
       <c r="K27" t="str">
+        <v/>
+      </c>
+      <c r="L27" t="str">
         <v/>
       </c>
     </row>
@@ -1859,15 +1941,18 @@
         <v/>
       </c>
       <c r="H28" t="str">
+        <v/>
+      </c>
+      <c r="I28" t="str">
         <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
       </c>
-      <c r="I28" t="str">
-        <v/>
-      </c>
       <c r="J28" t="str">
         <v/>
       </c>
       <c r="K28" t="str">
+        <v/>
+      </c>
+      <c r="L28" t="str">
         <v/>
       </c>
     </row>
@@ -1894,21 +1979,24 @@
         <v/>
       </c>
       <c r="H29" t="str">
+        <v/>
+      </c>
+      <c r="I29" t="str">
         <v>Watching only · all-you-can-eat wings</v>
       </c>
-      <c r="I29" t="str">
-        <v/>
-      </c>
       <c r="J29" t="str">
         <v/>
       </c>
       <c r="K29" t="str">
+        <v/>
+      </c>
+      <c r="L29" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K29"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/docs/Silent-Auction-Import.xlsx
+++ b/docs/Silent-Auction-Import.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Items" sheetId="1" r:id="rId1"/>
-    <sheet name="Tickets" sheetId="2" r:id="rId2"/>
-    <sheet name="Config" sheetId="3" r:id="rId3"/>
+    <sheet name="Config" sheetId="1" r:id="rId1"/>
+    <sheet name="Items" sheetId="2" r:id="rId2"/>
+    <sheet name="Tickets" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
@@ -399,22 +399,87 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B9"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>Key</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Value</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>event_name</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Company Picnic Silent Auction</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>timezone</v>
+      </c>
+      <c r="B3" t="str">
+        <v>America/New_York</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>event_date</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-07-18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>extension_window_seconds</v>
+      </c>
+      <c r="B5" t="str">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ticket_cascade_start</v>
+      </c>
+      <c r="B6" t="str">
+        <v>7:00 PM</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>ticket_countdown_seconds</v>
+      </c>
+      <c r="B7" t="str">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>urgent_threshold_seconds</v>
+      </c>
+      <c r="B8" t="str">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>featured_item_id</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:M11"/>
-  <cols>
-    <col min="1" max="1" width="5.83203125" customWidth="1"/>
-    <col min="2" max="2" width="48.83203125" customWidth="1"/>
-    <col min="3" max="3" width="42.83203125" customWidth="1"/>
-    <col min="4" max="4" width="16.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="11.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" customWidth="1"/>
-    <col min="9" max="9" width="16.83203125" customWidth="1"/>
-    <col min="10" max="10" width="9.83203125" customWidth="1"/>
-    <col min="11" max="11" width="16.83203125" customWidth="1"/>
-    <col min="12" max="12" width="7.83203125" customWidth="1"/>
-    <col min="13" max="13" width="10.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -458,22 +523,16 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2">
+      <c r="A2" t="str">
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>E-Bike — Uneek Step-Through Mr. Cruiser 750W</v>
-      </c>
-      <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2" t="str">
-        <v/>
-      </c>
-      <c r="E2">
+        <v>E-Bike â Uneek Step-Through Mr. Cruiser 750W</v>
+      </c>
+      <c r="E2" t="str">
         <v>200</v>
       </c>
-      <c r="F2">
+      <c r="F2" t="str">
         <v>1500</v>
       </c>
       <c r="G2" t="str">
@@ -482,39 +541,18 @@
       <c r="H2" t="str">
         <v>6:00 PM</v>
       </c>
-      <c r="I2" t="str">
-        <v/>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
-      </c>
-      <c r="M2" t="str">
-        <v/>
-      </c>
     </row>
     <row r="3">
-      <c r="A3">
+      <c r="A3" t="str">
         <v>2</v>
       </c>
       <c r="B3" t="str">
         <v>Flag Croquet</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3" t="str">
-        <v/>
-      </c>
-      <c r="E3">
+      <c r="E3" t="str">
         <v>150</v>
       </c>
-      <c r="F3">
+      <c r="F3" t="str">
         <v>550</v>
       </c>
       <c r="G3" t="str">
@@ -523,24 +561,9 @@
       <c r="H3" t="str">
         <v>6:05 PM</v>
       </c>
-      <c r="I3" t="str">
-        <v/>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
-      </c>
-      <c r="M3" t="str">
-        <v/>
-      </c>
     </row>
     <row r="4">
-      <c r="A4">
+      <c r="A4" t="str">
         <v>3</v>
       </c>
       <c r="B4" t="str">
@@ -549,13 +572,10 @@
       <c r="C4" t="str">
         <v>Donated by Keim</v>
       </c>
-      <c r="D4" t="str">
-        <v/>
-      </c>
-      <c r="E4">
+      <c r="E4" t="str">
         <v>100</v>
       </c>
-      <c r="F4">
+      <c r="F4" t="str">
         <v>850</v>
       </c>
       <c r="G4" t="str">
@@ -564,39 +584,21 @@
       <c r="H4" t="str">
         <v>6:10 PM</v>
       </c>
-      <c r="I4" t="str">
-        <v/>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
-      </c>
-      <c r="M4" t="str">
-        <v/>
-      </c>
     </row>
     <row r="5">
-      <c r="A5">
+      <c r="A5" t="str">
         <v>4</v>
       </c>
       <c r="B5" t="str">
         <v>Breville Barista Express Espresso Machine (MES870XL)</v>
       </c>
       <c r="C5" t="str">
-        <v>Brushed stainless steel · Amazon</v>
-      </c>
-      <c r="D5" t="str">
-        <v/>
-      </c>
-      <c r="E5">
+        <v>Brushed stainless steel Â· Amazon</v>
+      </c>
+      <c r="E5" t="str">
         <v>100</v>
       </c>
-      <c r="F5">
+      <c r="F5" t="str">
         <v>510</v>
       </c>
       <c r="G5" t="str">
@@ -605,39 +607,21 @@
       <c r="H5" t="str">
         <v>6:15 PM</v>
       </c>
-      <c r="I5" t="str">
-        <v/>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
-      </c>
-      <c r="M5" t="str">
-        <v/>
-      </c>
     </row>
     <row r="6">
-      <c r="A6">
+      <c r="A6" t="str">
         <v>5</v>
       </c>
       <c r="B6" t="str">
         <v>Ruger American Gen II .400 Legend Bolt-Action</v>
       </c>
       <c r="C6" t="str">
-        <v>With Hawke 3×9 scope</v>
-      </c>
-      <c r="D6" t="str">
-        <v/>
-      </c>
-      <c r="E6">
+        <v>With Hawke 3Ã9 scope</v>
+      </c>
+      <c r="E6" t="str">
         <v>200</v>
       </c>
-      <c r="F6">
+      <c r="F6" t="str">
         <v>600</v>
       </c>
       <c r="G6" t="str">
@@ -646,24 +630,9 @@
       <c r="H6" t="str">
         <v>6:20 PM</v>
       </c>
-      <c r="I6" t="str">
-        <v/>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
-      </c>
-      <c r="M6" t="str">
-        <v/>
-      </c>
     </row>
     <row r="7">
-      <c r="A7">
+      <c r="A7" t="str">
         <v>6</v>
       </c>
       <c r="B7" t="str">
@@ -672,13 +641,10 @@
       <c r="C7" t="str">
         <v>With SEVIIN GF series reel</v>
       </c>
-      <c r="D7" t="str">
-        <v/>
-      </c>
-      <c r="E7">
+      <c r="E7" t="str">
         <v>70</v>
       </c>
-      <c r="F7">
+      <c r="F7" t="str">
         <v>230</v>
       </c>
       <c r="G7" t="str">
@@ -687,24 +653,9 @@
       <c r="H7" t="str">
         <v>6:25 PM</v>
       </c>
-      <c r="I7" t="str">
-        <v/>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
-      </c>
-      <c r="M7" t="str">
-        <v/>
-      </c>
     </row>
     <row r="8">
-      <c r="A8">
+      <c r="A8" t="str">
         <v>7</v>
       </c>
       <c r="B8" t="str">
@@ -713,13 +664,10 @@
       <c r="C8" t="str">
         <v>Scope and 3 arrows</v>
       </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8">
+      <c r="E8" t="str">
         <v>300</v>
       </c>
-      <c r="F8">
+      <c r="F8" t="str">
         <v>800</v>
       </c>
       <c r="G8" t="str">
@@ -728,24 +676,9 @@
       <c r="H8" t="str">
         <v>6:30 PM</v>
       </c>
-      <c r="I8" t="str">
-        <v/>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
-      </c>
-      <c r="M8" t="str">
-        <v/>
-      </c>
     </row>
     <row r="9">
-      <c r="A9">
+      <c r="A9" t="str">
         <v>8</v>
       </c>
       <c r="B9" t="str">
@@ -754,13 +687,10 @@
       <c r="C9" t="str">
         <v>Donated by David Yoder (SC)</v>
       </c>
-      <c r="D9" t="str">
-        <v/>
-      </c>
-      <c r="E9">
+      <c r="E9" t="str">
         <v>50</v>
       </c>
-      <c r="F9">
+      <c r="F9" t="str">
         <v>110</v>
       </c>
       <c r="G9" t="str">
@@ -769,39 +699,21 @@
       <c r="H9" t="str">
         <v>6:35 PM</v>
       </c>
-      <c r="I9" t="str">
-        <v/>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
-      </c>
-      <c r="M9" t="str">
-        <v/>
-      </c>
     </row>
     <row r="10">
-      <c r="A10">
+      <c r="A10" t="str">
         <v>21</v>
       </c>
       <c r="B10" t="str">
-        <v>20 lbs Link Sausage — Winesburg Meats</v>
+        <v>20 lbs Link Sausage â Winesburg Meats</v>
       </c>
       <c r="C10" t="str">
         <v>Donated by Eddie Troyer</v>
       </c>
-      <c r="D10" t="str">
-        <v/>
-      </c>
-      <c r="E10">
+      <c r="E10" t="str">
         <v>30</v>
       </c>
-      <c r="F10">
+      <c r="F10" t="str">
         <v>100</v>
       </c>
       <c r="G10" t="str">
@@ -810,39 +722,21 @@
       <c r="H10" t="str">
         <v>6:40 PM</v>
       </c>
-      <c r="I10" t="str">
-        <v/>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
-      </c>
-      <c r="M10" t="str">
-        <v/>
-      </c>
     </row>
     <row r="11">
-      <c r="A11">
+      <c r="A11" t="str">
         <v>31</v>
       </c>
       <c r="B11" t="str">
         <v>1-Day Early-Season Bow Hunt at Shorty &amp; Bert's</v>
       </c>
       <c r="C11" t="str">
-        <v>Donated by Shorty &amp; Bert · Kenny Troyer provides transportation</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11">
+        <v>Donated by Shorty &amp; Bert Â· Kenny Troyer provides transportation</v>
+      </c>
+      <c r="E11" t="str">
         <v>100</v>
       </c>
-      <c r="F11">
+      <c r="F11" t="str">
         <v>240</v>
       </c>
       <c r="G11" t="str">
@@ -850,21 +744,6 @@
       </c>
       <c r="H11" t="str">
         <v>6:45 PM</v>
-      </c>
-      <c r="I11" t="str">
-        <v/>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
-      </c>
-      <c r="M11" t="str">
-        <v/>
       </c>
     </row>
   </sheetData>
@@ -874,23 +753,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L29"/>
-  <cols>
-    <col min="1" max="1" width="30.83203125" customWidth="1"/>
-    <col min="2" max="2" width="20.83203125" customWidth="1"/>
-    <col min="3" max="3" width="16.83203125" customWidth="1"/>
-    <col min="4" max="4" width="11.83203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="14.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="48.83203125" customWidth="1"/>
-    <col min="10" max="10" width="16.83203125" customWidth="1"/>
-    <col min="11" max="11" width="7.83203125" customWidth="1"/>
-    <col min="12" max="12" width="10.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:M29"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -900,33 +765,36 @@
         <v>Label</v>
       </c>
       <c r="C1" t="str">
+        <v>Seats</v>
+      </c>
+      <c r="D1" t="str">
         <v>Image URL</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>Starting Bid</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Current Bid</v>
       </c>
-      <c r="F1" t="str">
+      <c r="G1" t="str">
         <v>High Bidder</v>
       </c>
-      <c r="G1" t="str">
+      <c r="H1" t="str">
         <v>Cascade Start</v>
       </c>
-      <c r="H1" t="str">
+      <c r="I1" t="str">
         <v>Last Bid Time</v>
       </c>
-      <c r="I1" t="str">
+      <c r="J1" t="str">
         <v>Notes</v>
       </c>
-      <c r="J1" t="str">
+      <c r="K1" t="str">
         <v>Winner Phone</v>
       </c>
-      <c r="K1" t="str">
+      <c r="L1" t="str">
         <v>Paid?</v>
       </c>
-      <c r="L1" t="str">
+      <c r="M1" t="str">
         <v>Picked Up?</v>
       </c>
     </row>
@@ -938,34 +806,22 @@
         <v>1 of 12</v>
       </c>
       <c r="C2" t="str">
-        <v/>
-      </c>
-      <c r="D2">
-        <v>50</v>
-      </c>
-      <c r="E2">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="F2" t="str">
+        <v>80</v>
+      </c>
+      <c r="G2" t="str">
         <v>Matt Hershberger</v>
       </c>
-      <c r="G2" t="str">
-        <v>7:00 PM</v>
-      </c>
       <c r="H2" t="str">
-        <v/>
+        <v>6:00 PM</v>
       </c>
       <c r="I2" t="str">
+        <v>2026-06-12T08:10:02-07:00</v>
+      </c>
+      <c r="J2" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J2" t="str">
-        <v/>
-      </c>
-      <c r="K2" t="str">
-        <v/>
-      </c>
-      <c r="L2" t="str">
-        <v/>
       </c>
     </row>
     <row r="3">
@@ -975,35 +831,20 @@
       <c r="B3" t="str">
         <v>2 of 12</v>
       </c>
-      <c r="C3" t="str">
-        <v/>
-      </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-      <c r="E3">
-        <v>50</v>
-      </c>
       <c r="F3" t="str">
+        <v>90</v>
+      </c>
+      <c r="G3" t="str">
         <v>Ken Miller</v>
       </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
       <c r="H3" t="str">
-        <v/>
+        <v>6:01 PM</v>
       </c>
       <c r="I3" t="str">
+        <v>2026-06-12T08:10:21-07:00</v>
+      </c>
+      <c r="J3" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v/>
       </c>
     </row>
     <row r="4">
@@ -1013,35 +854,17 @@
       <c r="B4" t="str">
         <v>3 of 12</v>
       </c>
-      <c r="C4" t="str">
-        <v/>
-      </c>
-      <c r="D4">
-        <v>20</v>
-      </c>
-      <c r="E4">
+      <c r="F4" t="str">
         <v>30</v>
       </c>
-      <c r="F4" t="str">
+      <c r="G4" t="str">
         <v>Chad Gerber</v>
       </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
       <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
+        <v>6:02 PM</v>
+      </c>
+      <c r="J4" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v/>
       </c>
     </row>
     <row r="5">
@@ -1051,35 +874,17 @@
       <c r="B5" t="str">
         <v>4 of 12</v>
       </c>
-      <c r="C5" t="str">
-        <v/>
-      </c>
-      <c r="D5">
-        <v>10</v>
-      </c>
-      <c r="E5">
+      <c r="F5" t="str">
         <v>20</v>
       </c>
-      <c r="F5" t="str">
+      <c r="G5" t="str">
         <v>Grant Gingerich</v>
       </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
       <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
+        <v>6:03 PM</v>
+      </c>
+      <c r="J5" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v/>
       </c>
     </row>
     <row r="6">
@@ -1089,35 +894,17 @@
       <c r="B6" t="str">
         <v>5 of 12</v>
       </c>
-      <c r="C6" t="str">
-        <v/>
-      </c>
-      <c r="D6">
+      <c r="F6" t="str">
         <v>20</v>
       </c>
-      <c r="E6">
-        <v>20</v>
-      </c>
-      <c r="F6" t="str">
+      <c r="G6" t="str">
         <v>David Lee</v>
       </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
       <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
+        <v>6:04 PM</v>
+      </c>
+      <c r="J6" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v/>
       </c>
     </row>
     <row r="7">
@@ -1127,35 +914,17 @@
       <c r="B7" t="str">
         <v>6 of 12</v>
       </c>
-      <c r="C7" t="str">
-        <v/>
-      </c>
-      <c r="D7">
+      <c r="F7" t="str">
         <v>20</v>
       </c>
-      <c r="E7">
-        <v>20</v>
-      </c>
-      <c r="F7" t="str">
+      <c r="G7" t="str">
         <v>Ivan Yoder</v>
       </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
       <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
+        <v>6:05 PM</v>
+      </c>
+      <c r="J7" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v/>
       </c>
     </row>
     <row r="8">
@@ -1165,35 +934,17 @@
       <c r="B8" t="str">
         <v>7 of 12</v>
       </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8">
+      <c r="F8" t="str">
         <v>20</v>
       </c>
-      <c r="E8">
-        <v>20</v>
-      </c>
-      <c r="F8" t="str">
+      <c r="G8" t="str">
         <v>Jacob Miller</v>
       </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
       <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
+        <v>6:06 PM</v>
+      </c>
+      <c r="J8" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v/>
       </c>
     </row>
     <row r="9">
@@ -1203,35 +954,17 @@
       <c r="B9" t="str">
         <v>8 of 12</v>
       </c>
-      <c r="C9" t="str">
-        <v/>
-      </c>
-      <c r="D9">
+      <c r="F9" t="str">
         <v>20</v>
       </c>
-      <c r="E9">
-        <v>20</v>
-      </c>
-      <c r="F9" t="str">
+      <c r="G9" t="str">
         <v>Jacob Miller</v>
       </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
       <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
+        <v>6:07 PM</v>
+      </c>
+      <c r="J9" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v/>
       </c>
     </row>
     <row r="10">
@@ -1241,35 +974,17 @@
       <c r="B10" t="str">
         <v>9 of 12</v>
       </c>
-      <c r="C10" t="str">
-        <v/>
-      </c>
-      <c r="D10">
+      <c r="F10" t="str">
         <v>20</v>
       </c>
-      <c r="E10">
-        <v>20</v>
-      </c>
-      <c r="F10" t="str">
+      <c r="G10" t="str">
         <v>Jared Hanni</v>
       </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
       <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
+        <v>6:08 PM</v>
+      </c>
+      <c r="J10" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v/>
       </c>
     </row>
     <row r="11">
@@ -1279,35 +994,17 @@
       <c r="B11" t="str">
         <v>10 of 12</v>
       </c>
-      <c r="C11" t="str">
-        <v/>
-      </c>
-      <c r="D11">
+      <c r="F11" t="str">
         <v>40</v>
       </c>
-      <c r="E11">
-        <v>40</v>
-      </c>
-      <c r="F11" t="str">
+      <c r="G11" t="str">
         <v>Myron Yoder</v>
       </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
       <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
+        <v>6:09 PM</v>
+      </c>
+      <c r="J11" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v/>
       </c>
     </row>
     <row r="12">
@@ -1317,35 +1014,17 @@
       <c r="B12" t="str">
         <v>11 of 12</v>
       </c>
-      <c r="C12" t="str">
-        <v/>
-      </c>
-      <c r="D12">
+      <c r="F12" t="str">
         <v>30</v>
       </c>
-      <c r="E12">
-        <v>30</v>
-      </c>
-      <c r="F12" t="str">
+      <c r="G12" t="str">
         <v>John Yoder</v>
       </c>
-      <c r="G12" t="str">
-        <v/>
-      </c>
       <c r="H12" t="str">
-        <v/>
-      </c>
-      <c r="I12" t="str">
+        <v>6:10 PM</v>
+      </c>
+      <c r="J12" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J12" t="str">
-        <v/>
-      </c>
-      <c r="K12" t="str">
-        <v/>
-      </c>
-      <c r="L12" t="str">
-        <v/>
       </c>
     </row>
     <row r="13">
@@ -1355,187 +1034,91 @@
       <c r="B13" t="str">
         <v>12 of 12</v>
       </c>
-      <c r="C13" t="str">
-        <v/>
-      </c>
-      <c r="D13">
+      <c r="F13" t="str">
         <v>30</v>
       </c>
-      <c r="E13">
-        <v>30</v>
-      </c>
-      <c r="F13" t="str">
+      <c r="G13" t="str">
         <v>Eddie Troyer</v>
       </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
       <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
+        <v>6:11 PM</v>
+      </c>
+      <c r="J13" t="str">
         <v>Lunch on Jul 23</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Rib Dinner — Peter &amp; Aaron</v>
+        <v>Rib Dinner â Peter &amp; Aaron Troyer</v>
       </c>
       <c r="B14" t="str">
         <v>1 of 4</v>
       </c>
       <c r="C14" t="str">
-        <v/>
-      </c>
-      <c r="D14">
-        <v>20</v>
-      </c>
-      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14" t="str">
         <v>150</v>
       </c>
-      <c r="F14" t="str">
+      <c r="G14" t="str">
         <v>Matt Janzi</v>
       </c>
-      <c r="G14" t="str">
-        <v>7:20 PM</v>
-      </c>
       <c r="H14" t="str">
-        <v/>
-      </c>
-      <c r="I14" t="str">
+        <v>6:02 PM</v>
+      </c>
+      <c r="J14" t="str">
         <v>@ Peter's house 7/10 at 5:30. Campfire after, weather permitting</v>
-      </c>
-      <c r="J14" t="str">
-        <v/>
-      </c>
-      <c r="K14" t="str">
-        <v/>
-      </c>
-      <c r="L14" t="str">
-        <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Rib Dinner — Peter &amp; Aaron</v>
+        <v>Rib Dinner â Peter &amp; Aaron Troyer</v>
       </c>
       <c r="B15" t="str">
         <v>2 of 4</v>
       </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15">
-        <v>50</v>
-      </c>
-      <c r="E15">
+      <c r="F15" t="str">
         <v>200</v>
       </c>
-      <c r="F15" t="str">
+      <c r="G15" t="str">
         <v>Lamar Shrock</v>
       </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
       <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
+        <v>6:03 PM</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Rib Dinner — Peter &amp; Aaron</v>
+        <v>Rib Dinner â Peter &amp; Aaron Troyer</v>
       </c>
       <c r="B16" t="str">
         <v>3 of 4</v>
       </c>
-      <c r="C16" t="str">
-        <v/>
-      </c>
-      <c r="D16">
-        <v>150</v>
-      </c>
-      <c r="E16">
+      <c r="F16" t="str">
         <v>200</v>
       </c>
-      <c r="F16" t="str">
+      <c r="G16" t="str">
         <v>Albert Yoder</v>
       </c>
-      <c r="G16" t="str">
-        <v/>
-      </c>
       <c r="H16" t="str">
-        <v/>
-      </c>
-      <c r="I16" t="str">
-        <v/>
-      </c>
-      <c r="J16" t="str">
-        <v/>
-      </c>
-      <c r="K16" t="str">
-        <v/>
-      </c>
-      <c r="L16" t="str">
-        <v/>
+        <v>6:04 PM</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Rib Dinner — Peter &amp; Aaron</v>
+        <v>Rib Dinner â Peter &amp; Aaron Troyer</v>
       </c>
       <c r="B17" t="str">
         <v>4 of 4</v>
       </c>
-      <c r="C17" t="str">
-        <v/>
-      </c>
-      <c r="D17">
+      <c r="F17" t="str">
         <v>150</v>
       </c>
-      <c r="E17">
-        <v>150</v>
-      </c>
-      <c r="F17" t="str">
+      <c r="G17" t="str">
         <v>Brian Barkman</v>
       </c>
-      <c r="G17" t="str">
-        <v/>
-      </c>
       <c r="H17" t="str">
-        <v/>
-      </c>
-      <c r="I17" t="str">
-        <v/>
-      </c>
-      <c r="J17" t="str">
-        <v/>
-      </c>
-      <c r="K17" t="str">
-        <v/>
-      </c>
-      <c r="L17" t="str">
-        <v/>
+        <v>6:05 PM</v>
       </c>
     </row>
     <row r="18">
@@ -1546,34 +1129,19 @@
         <v>1 of 3</v>
       </c>
       <c r="C18" t="str">
-        <v/>
-      </c>
-      <c r="D18">
-        <v>30</v>
-      </c>
-      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18" t="str">
         <v>120</v>
       </c>
-      <c r="F18" t="str">
+      <c r="G18" t="str">
         <v>Aaron Troyer</v>
       </c>
-      <c r="G18" t="str">
-        <v>7:35 PM</v>
-      </c>
       <c r="H18" t="str">
-        <v/>
-      </c>
-      <c r="I18" t="str">
-        <v>Donated by Dennis · Sometime in July</v>
+        <v>6:08 PM</v>
       </c>
       <c r="J18" t="str">
-        <v/>
-      </c>
-      <c r="K18" t="str">
-        <v/>
-      </c>
-      <c r="L18" t="str">
-        <v/>
+        <v>Donated by Dennis Â· Sometime in July</v>
       </c>
     </row>
     <row r="19">
@@ -1583,35 +1151,17 @@
       <c r="B19" t="str">
         <v>2 of 3</v>
       </c>
-      <c r="C19" t="str">
-        <v/>
-      </c>
-      <c r="D19">
-        <v>60</v>
-      </c>
-      <c r="E19">
+      <c r="F19" t="str">
         <v>120</v>
       </c>
-      <c r="F19" t="str">
+      <c r="G19" t="str">
         <v>Aaron Troyer</v>
       </c>
-      <c r="G19" t="str">
-        <v/>
-      </c>
       <c r="H19" t="str">
-        <v/>
-      </c>
-      <c r="I19" t="str">
-        <v>Donated by Dennis · Sometime in July</v>
+        <v>6:09 PM</v>
       </c>
       <c r="J19" t="str">
-        <v/>
-      </c>
-      <c r="K19" t="str">
-        <v/>
-      </c>
-      <c r="L19" t="str">
-        <v/>
+        <v>Donated by Dennis Â· Sometime in July</v>
       </c>
     </row>
     <row r="20">
@@ -1621,111 +1171,60 @@
       <c r="B20" t="str">
         <v>3 of 3</v>
       </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20">
-        <v>60</v>
-      </c>
-      <c r="E20">
+      <c r="F20" t="str">
         <v>100</v>
       </c>
-      <c r="F20" t="str">
+      <c r="G20" t="str">
         <v>Ivan Miller</v>
       </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
       <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v>Donated by Dennis · Sometime in July</v>
+        <v>6:10 PM</v>
       </c>
       <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
+        <v>Donated by Dennis Â· Sometime in July</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Kratzer Steak Dinner for 2</v>
+        <v>Charlie Steak Dinner for 2</v>
       </c>
       <c r="B21" t="str">
         <v>1 of 2</v>
       </c>
       <c r="C21" t="str">
-        <v/>
-      </c>
-      <c r="D21">
-        <v>40</v>
-      </c>
-      <c r="E21">
+        <v>2</v>
+      </c>
+      <c r="F21" t="str">
         <v>300</v>
       </c>
-      <c r="F21" t="str">
+      <c r="G21" t="str">
         <v>Dan D. I. Miller</v>
       </c>
-      <c r="G21" t="str">
-        <v>7:45 PM</v>
-      </c>
       <c r="H21" t="str">
-        <v/>
-      </c>
-      <c r="I21" t="str">
+        <v>6:12 PM</v>
+      </c>
+      <c r="J21" t="str">
         <v>Donated by Charles &amp; Gloria Kratzer</v>
-      </c>
-      <c r="J21" t="str">
-        <v/>
-      </c>
-      <c r="K21" t="str">
-        <v/>
-      </c>
-      <c r="L21" t="str">
-        <v/>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Kratzer Steak Dinner for 2</v>
+        <v>Charlie Steak Dinner for 2</v>
       </c>
       <c r="B22" t="str">
         <v>2 of 2</v>
       </c>
-      <c r="C22" t="str">
-        <v/>
-      </c>
-      <c r="D22">
-        <v>30</v>
-      </c>
-      <c r="E22">
+      <c r="F22" t="str">
         <v>300</v>
       </c>
-      <c r="F22" t="str">
+      <c r="G22" t="str">
         <v>Dan D. I. Miller</v>
       </c>
-      <c r="G22" t="str">
-        <v/>
-      </c>
       <c r="H22" t="str">
-        <v/>
-      </c>
-      <c r="I22" t="str">
+        <v>6:13 PM</v>
+      </c>
+      <c r="J22" t="str">
         <v>Donated by Charles &amp; Gloria Kratzer</v>
-      </c>
-      <c r="J22" t="str">
-        <v/>
-      </c>
-      <c r="K22" t="str">
-        <v/>
-      </c>
-      <c r="L22" t="str">
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -1736,34 +1235,19 @@
         <v>1 of 6</v>
       </c>
       <c r="C23" t="str">
-        <v/>
-      </c>
-      <c r="D23">
-        <v>50</v>
-      </c>
-      <c r="E23">
+        <v>6</v>
+      </c>
+      <c r="F23" t="str">
         <v>60</v>
       </c>
-      <c r="F23" t="str">
+      <c r="G23" t="str">
         <v>Eric McGlumphy</v>
       </c>
-      <c r="G23" t="str">
-        <v>7:55 PM</v>
-      </c>
       <c r="H23" t="str">
-        <v/>
-      </c>
-      <c r="I23" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:14 PM</v>
       </c>
       <c r="J23" t="str">
-        <v/>
-      </c>
-      <c r="K23" t="str">
-        <v/>
-      </c>
-      <c r="L23" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="24">
@@ -1773,35 +1257,17 @@
       <c r="B24" t="str">
         <v>2 of 6</v>
       </c>
-      <c r="C24" t="str">
-        <v/>
-      </c>
-      <c r="D24">
+      <c r="F24" t="str">
         <v>50</v>
       </c>
-      <c r="E24">
-        <v>50</v>
-      </c>
-      <c r="F24" t="str">
+      <c r="G24" t="str">
         <v>Matt Hershberger</v>
       </c>
-      <c r="G24" t="str">
-        <v/>
-      </c>
       <c r="H24" t="str">
-        <v/>
-      </c>
-      <c r="I24" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:15 PM</v>
       </c>
       <c r="J24" t="str">
-        <v/>
-      </c>
-      <c r="K24" t="str">
-        <v/>
-      </c>
-      <c r="L24" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="25">
@@ -1811,35 +1277,17 @@
       <c r="B25" t="str">
         <v>3 of 6</v>
       </c>
-      <c r="C25" t="str">
-        <v/>
-      </c>
-      <c r="D25">
+      <c r="F25" t="str">
         <v>50</v>
       </c>
-      <c r="E25">
-        <v>50</v>
-      </c>
-      <c r="F25" t="str">
+      <c r="G25" t="str">
         <v>Owen Yoder</v>
       </c>
-      <c r="G25" t="str">
-        <v/>
-      </c>
       <c r="H25" t="str">
-        <v/>
-      </c>
-      <c r="I25" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:16 PM</v>
       </c>
       <c r="J25" t="str">
-        <v/>
-      </c>
-      <c r="K25" t="str">
-        <v/>
-      </c>
-      <c r="L25" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="26">
@@ -1849,35 +1297,17 @@
       <c r="B26" t="str">
         <v>4 of 6</v>
       </c>
-      <c r="C26" t="str">
-        <v/>
-      </c>
-      <c r="D26">
+      <c r="F26" t="str">
         <v>75</v>
       </c>
-      <c r="E26">
-        <v>75</v>
-      </c>
-      <c r="F26" t="str">
+      <c r="G26" t="str">
         <v>Rueben Yoder</v>
       </c>
-      <c r="G26" t="str">
-        <v/>
-      </c>
       <c r="H26" t="str">
-        <v/>
-      </c>
-      <c r="I26" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:17 PM</v>
       </c>
       <c r="J26" t="str">
-        <v/>
-      </c>
-      <c r="K26" t="str">
-        <v/>
-      </c>
-      <c r="L26" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="27">
@@ -1887,35 +1317,17 @@
       <c r="B27" t="str">
         <v>5 of 6</v>
       </c>
-      <c r="C27" t="str">
-        <v/>
-      </c>
-      <c r="D27">
+      <c r="F27" t="str">
         <v>150</v>
       </c>
-      <c r="E27">
-        <v>150</v>
-      </c>
-      <c r="F27" t="str">
+      <c r="G27" t="str">
         <v>Aaron Troyer</v>
       </c>
-      <c r="G27" t="str">
-        <v/>
-      </c>
       <c r="H27" t="str">
-        <v/>
-      </c>
-      <c r="I27" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:18 PM</v>
       </c>
       <c r="J27" t="str">
-        <v/>
-      </c>
-      <c r="K27" t="str">
-        <v/>
-      </c>
-      <c r="L27" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="28">
@@ -1925,165 +1337,45 @@
       <c r="B28" t="str">
         <v>6 of 6</v>
       </c>
-      <c r="C28" t="str">
-        <v/>
-      </c>
-      <c r="D28">
+      <c r="F28" t="str">
         <v>150</v>
       </c>
-      <c r="E28">
-        <v>150</v>
-      </c>
-      <c r="F28" t="str">
+      <c r="G28" t="str">
         <v>Mark Hochstetler</v>
       </c>
-      <c r="G28" t="str">
-        <v/>
-      </c>
       <c r="H28" t="str">
-        <v/>
-      </c>
-      <c r="I28" t="str">
-        <v>Donated by Albert &amp; Derrick W · 2 people per ticket</v>
+        <v>6:19 PM</v>
       </c>
       <c r="J28" t="str">
-        <v/>
-      </c>
-      <c r="K28" t="str">
-        <v/>
-      </c>
-      <c r="L28" t="str">
-        <v/>
+        <v>Donated by Albert &amp; Derrick W Â· 2 people per ticket</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Wings &amp; Bucket Golf at Albert's</v>
+        <v>Wings &amp; Bucket Golf â Spectator</v>
       </c>
       <c r="B29" t="str">
         <v>Spectator (2 people)</v>
       </c>
       <c r="C29" t="str">
-        <v/>
-      </c>
-      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="F29" t="str">
         <v>50</v>
       </c>
-      <c r="E29">
-        <v>50</v>
-      </c>
-      <c r="F29" t="str">
+      <c r="G29" t="str">
         <v>Eddie Troyer</v>
       </c>
-      <c r="G29" t="str">
-        <v/>
-      </c>
       <c r="H29" t="str">
-        <v/>
-      </c>
-      <c r="I29" t="str">
-        <v>Watching only · all-you-can-eat wings</v>
+        <v>6:20 PM</v>
       </c>
       <c r="J29" t="str">
-        <v/>
-      </c>
-      <c r="K29" t="str">
-        <v/>
-      </c>
-      <c r="L29" t="str">
-        <v/>
+        <v>Watching only Â· all-you-can-eat wings</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L29"/>
-  </ignoredErrors>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
-  <cols>
-    <col min="1" max="1" width="26.83203125" customWidth="1"/>
-    <col min="2" max="2" width="32.83203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>Key</v>
-      </c>
-      <c r="B1" t="str">
-        <v>Value</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="str">
-        <v>event_name</v>
-      </c>
-      <c r="B2" t="str">
-        <v>Company Picnic Silent Auction</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>timezone</v>
-      </c>
-      <c r="B3" t="str">
-        <v>America/New_York</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>event_date</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-07-18</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>extension_window_seconds</v>
-      </c>
-      <c r="B5">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ticket_cascade_start</v>
-      </c>
-      <c r="B6" t="str">
-        <v>7:00 PM</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>ticket_countdown_seconds</v>
-      </c>
-      <c r="B7">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>urgent_threshold_seconds</v>
-      </c>
-      <c r="B8">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>featured_item_id</v>
-      </c>
-      <c r="B9" t="str">
-        <v/>
-      </c>
-    </row>
-  </sheetData>
-  <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:B9"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M29"/>
   </ignoredErrors>
 </worksheet>
 </file>